--- a/TESTS/zlit_9_bredberi_451.xlsx
+++ b/TESTS/zlit_9_bredberi_451.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -603,6 +608,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -645,6 +655,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -687,6 +702,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -813,6 +843,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -958,7 +1008,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Небезпека знищення культури і думки — цензура і маніпуляції</t>
+          <t>Небезпека знищення культури і думки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -979,6 +1029,11 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1023,6 +1078,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1042,7 +1102,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Суспільство без книг — духовно мертве</t>
+          <t>Суспільство без книг</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1063,6 +1123,11 @@
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1107,6 +1172,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1149,6 +1219,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1191,6 +1266,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1233,6 +1313,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1275,6 +1360,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1317,6 +1407,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1359,6 +1454,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1401,6 +1501,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1443,6 +1548,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1485,6 +1595,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1527,6 +1642,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1569,6 +1689,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1611,6 +1736,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1653,6 +1783,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1695,6 +1830,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1737,6 +1877,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1779,6 +1924,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1821,6 +1971,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1835,16 +1990,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1869,16 +2027,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1903,16 +2064,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,29 +2096,32 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>У романі Бредбері пожежники гасять пожежі.</t>
+          <t>У романі Бредбері пожежники НЕ гасять пожежі — вони їх розпалюють, спалюючи книги.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>А</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Пожежники у «451 градусі» гасять вогонь, а не спалюють книги.</t>
+          <t>Головна функція пожежників у «451 градусі» — знищувати книги, а не гасити вогонь.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>А</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чи гасять пожежники вогонь у романі «451 градус»?</t>
+          <t>У «451 градусі» пожежники виконують звичайну роботу — гасять пожежі.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Б</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Головна ідея «451 градуса» — небезпека знищення книг і вільної думки.</t>
+          <t>Роман Бредбері застерігає: знищення книг і вільної думки веде суспільство до духовної катастрофи.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>«451 градус» застерігає від цензури і знищення культури.</t>
+          <t>«451 градус» є антиутопією про небезпеку цензури і тотального контролю над думкою.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Чи є небезпека цензури головною ідеєю «451 градуса»?</t>
+          <t>«451 градус» є оптимістичним романом про щасливе суспільство без книг.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2253,6 +2445,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
